--- a/docs/LALKITAB_MASTER.xlsx
+++ b/docs/LALKITAB_MASTER.xlsx
@@ -17,7 +17,9 @@
     <sheet name="MASNUI" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="RIN" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="MERE_NIYAM" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="SCOPE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SYSTEM" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="FAISLE" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SCOPE" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -171,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -222,6 +224,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -589,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -888,24 +899,64 @@
       <c r="A21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>इंजन की जाँच — 18 खामियाँ, माप सहित</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>🔴 पढ़ें</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>FAISLE</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>3 फ़ैसले जो बनाने से पहले चाहिए</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>🟡 जाँचें</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>SCOPE</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>6 प्रस्तुति-निर्णय</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>🔵 सिफ़ारिश</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>📌 इस दौर में क्या नया हुआ — मैंने आपका सारा दिया हुआ डेटा दोबारा आपस में भिड़ाकर जाँचा। चार नई गलतियाँ निकलीं, और उनमें से एक मेरी अपनी थी: 'कच्चा घर' की जो परिभाषा मैंने पिछली बार खुद बनाई थी, वह आपकी दी हुई सूची से 18 में से 0 जगह मिलती है — यानी वह पूरी तरह ग़लत थी। अब आपकी सूची लगेगी। विवरण SUDHAR शीट में।</t>
         </is>
@@ -914,8 +965,8 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A23:D23"/>
     <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A10:D10"/>
   </mergeCells>
@@ -1215,6 +1266,695 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="76" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🔴 इंजन की जाँच — क्या यह सही फलादेश व उपाय दे पाएगा?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>इंजन की 2200 पंक्तियाँ पढ़ीं, फिर चलाकर मापा। हर आँकड़ा असली गणना से है, राय नहीं।</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>दर्जा</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>खामी</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>विवरण व माप</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>ठीक होने पर क्या सुधरेगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>गंभीर</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>उच्च/नीच असली राशि से जाँचा जा रहा है, टेवा के भाव से नहीं</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>लाल किताब का टेवा स्थिर है — भाव 1 हमेशा मेष। आपने उच्च-नीच की सूची भाव के हिसाब से दी थी (सूर्य भाव 1 · चन्द्र भाव 2 · मंगल भाव 10 …), पर कोड ग्रह की असली गोचर राशि देखता है। माप — 5,000 कुंडलियाँ / 45,000 ग्रह-पंक्तियाँ: 31.8% पंक्तियों का वर्गीकरण बदलता है; 95.5% कुंडलियों में कम से कम एक ग्रह अलग।</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>हर कुंडली का मूल वर्गीकरण सही होगा — यही सबसे बड़ा असर</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>गंभीर</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>राहु-केतु की उच्च/नीच कोड में पूरी तरह अलग</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>कोड: राहु उच्च वृष · नीच वृश्चिक। आपकी सूची: राहु उच्च भाव 3, 6 · नीच भाव 9, 12 (केतु उलटा)। बाकी सात ग्रहों में कोड व आपकी सूची मेल खाती है — केवल ये दो गलत हैं।</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>छाया-ग्रहों का फल सही बनेगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="62" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>गंभीर</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>टक्कर दोनों दिशाओं में लग रही है</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>आपका नियम एकतरफ़ा है (ग्रह अपने से आठवें को मारता है), पर takrav कॉलम में आगे का 8वाँ और पीछे का 8वाँ (= आगे का 6ठा) दोनों हैं और इंजन दोनों पर दंड लगाता है। माप — 20,000 कुंडलियाँ: 1,81,143 दंड लगे, 90,516 (ठीक 50%) गलत; 99% कुंडलियाँ प्रभावित।</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>आधे बेवजह के दंड हट जाएँगे</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>गंभीर</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>विंशोत्तरी दशा लाल किताब की उपाय-सूची चला रही है</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>स्कोर के दो सबसे बड़े अंक — महादशा +3, अंतर्दशा +2 — विंशोत्तरी से आते हैं। प्रमाण: एक ही कुंडली पर केवल विंशोत्तरी स्वामी बदलने से 'पहले ये उपाय करें' का पहला नाम हर बार बदल गया (सूर्य → शनि → शुक्र → केतु)। 35-साला दशा कोड में मौजूद है पर स्कोर में इस्तेमाल नहीं।</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>उपाय सही क्रम में आएँगे — यही निराशा की मुख्य वजह लगती है</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>गंभीर</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>पक्का घर उलटा लगा है — दोनों जगह</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>निष्कर्ष में पक्का घर = +1 शुभ; स्कोर में पक्का घर = −1 (उपाय कम ज़रूरी)। आपका नियम इसके ठीक उलटा है — पक्का = तीव्रता, शुभता नहीं। अशुभ ग्रह पक्के घर में हो तो बुरा असर पूरी ताकत से ⇒ उपाय ज़्यादा ज़रूरी।</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>अशुभ ग्रह छिपेंगे नहीं</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>गंभीर</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>PUKKA_GHAR तालिका ही गलत है</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>कोड की सूची कारक-भाव की अधूरी नकल है — बुध 7 (सही 6,7) · गुरु 9 (सही 2,5,9,11,12) · शनि 10 (सही 8,10)।</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>तीव्रता सही ग्रहों पर लगेगी</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="62" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>गंभीर</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>दृष्टि तालिका गलत — और वह पाँच जगह फैलती है</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>'हर भाव अपने से 6 आगे' वाली गलत तालिका से बनते हैं: दो ग्रहों का संबंध · कौन इस पर असर डालता है · यह किन पर डालता है · दृष्टि दृश्य · सोया भाव/ग्रह।</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>एक सुधार से पाँच नतीजे साफ़ होंगे</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>गंभीर</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>सोया ग्रह का नियम कभी चलता ही नहीं</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>माप: 1800 ग्रह-पंक्तियों में 0 ग्रह सोया निकला। पुरानी शर्त हमेशा सच रहती है।</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>सोया-जागृति व उसके उपाय चालू होंगे</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>अधूरा</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>कच्चा घर कहीं इस्तेमाल नहीं — 0 जगह</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>आपकी कच्चा-घर सूची कोड में है ही नहीं ⇒ 'फल अधूरा/कमज़ोर/देर से' वाला गुणक लगता ही नहीं।</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>कमज़ोरी सही दिखेगी</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>अधूरा</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>बुनियाद (जड़) का नियम — 0 जगह</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>neev कॉलम डेटा में है, कोड में एक बार भी नहीं पढ़ा जाता। 9→5 व 2→8 नहीं चलते।</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>जड़-शाखा का फल जुड़ेगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="62" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>अधूरा</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>मसनूई (कृत्रिम) ग्रह — 0 जगह</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>11 युतियाँ तय हो चुकी हैं पर कोड में masnui शब्द तक नहीं।</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>युति का असली अर्थ आएगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="62" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>अधूरा</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>मुकाबले के ग्रह — 0 जगह</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>भाव 8 में मंगल+शनि की एकतरफ़ा शत्रुता — कोई जाँच नहीं।</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>भाव 8 का फल सही बनेगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="62" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>अधूरा</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>sajhi_chot कॉलम — 0 जगह</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>डेटा में है, पढ़ा नहीं जाता। vishwasghat व achanak_chot केवल दिखाए जाते हैं, फलादेश में गिने नहीं जाते।</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>साझी चोट का नियम चालू होगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="62" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>उपाय</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>46% ग्रहों को कोई उपाय नहीं मिलता</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>माप: 1800 में से 822 ग्रह-पंक्तियों पर कोई उपाय नहीं। उपाय-योजना केवल 'अशुभ' या 'नीच' ग्रह लेती है; 'मध्यम' निष्कर्ष वाले 25% ग्रह पूरी तरह छूट जाते हैं — चाहे टक्कर लगी हो, चाहे दोष में हों।</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>हर नकारात्मक बात पर उपाय आएगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="62" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>उपाय</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>टक्कर खाए 40% ग्रहों को कोई उपाय नहीं</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>माप: 1413 ग्रह टक्कर खाते हैं (78%), इनमें 561 (40%) को कोई उपाय नहीं मिलता।</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>आपका अपना नियम पूरा होगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="62" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>उपाय</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>उपाय-प्राथमिकता में कच्चा/पक्का, टक्कर, दृष्टि — कुछ नहीं</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>स्कोर केवल 10 चीज़ें देखता है, और उनमें 2 सबसे बड़ी विंशोत्तरी से आती हैं।</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>प्राथमिकता भरोसेमंद बनेगी</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="62" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>डेटा</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>grah_chakra की ख़राब पंक्तियाँ स्कोर में चल रही हैं</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>'इस आयु-वर्ष में अशुभ वर्ष (+2)' उसी ashubh कॉलम से आता है जिसकी 3 पंक्तियाँ (शुक्र, शनि, राहु) ख़राब हैं ⇒ गलत उम्र पर चेतावनी।</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>चेतावनी सही वर्ष पर आएगी</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="62" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>डेटा</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>विशेष व क्रम कॉलम कच्चे रूप में दिख रहे हैं</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>गुरु '76वें वर्ष' (सही 16) · शुक्र खाली · क्रम कॉलम — तीनों स्क्रीन पर वैसे ही छपते हैं।</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>स्क्रीन पर गलत जानकारी नहीं दिखेगी</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>✅ अच्छी बात — ढाँचा मज़बूत है: डेटा अलग, गणना अलग, हर निष्कर्ष के साथ 'क्यों' दर्ज होता है, और उपाय का पूरा भंडार मौजूद है। 39 डेटा-खंडों में से ज़्यादातर सही हैं।</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>🎯 असली बात — गलतियाँ बिखरी नहीं, तीन जगह केंद्रित हैं: ① उच्च/नीच किस आधार पर ② दृष्टि व टक्कर की तालिका ③ उपाय-प्राथमिकता किस दशा से। ये तीन ठीक होते ही ऊपर की 18 में से 13 खामियाँ अपने-आप हल हो जाती हैं।</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A24:E24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🟡 3 फ़ैसले — इनके बिना मैं शुरू नहीं करूँगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ये तीनों बड़े असर वाले हैं, इसलिए आपके शब्द के बिना कोड नहीं छूऊँगा।</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>फ़ैसला</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>बात क्या है</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>मेरी सिफ़ारिश</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>आपका उत्तर</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>टिप्पणी</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>उच्च/नीच किससे तय हो?</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>(क) टेवा के भाव से — भाव 1 = मेष, तो भाव 1 में बैठा सूर्य उच्च। (ख) ग्रह की असली गोचर राशि से — जैसा अभी कोड में है। असर: 32% ग्रह-पंक्तियाँ व 95% कुंडलियाँ बदलेंगी।</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>(क) भाव से — आपकी दी हुई सूची इसी रूप में थी</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr"/>
+      <c r="F5" s="17" t="inlineStr"/>
+    </row>
+    <row r="6" ht="62" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>टक्कर किस दिशा में?</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>केवल 8वाँ (एकतरफ़ा, आपके कहे अनुसार), या 6ठा भी? अभी दोनों लगते हैं और आधे दंड बेवजह हैं।</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>केवल 8वाँ — यह आपके 'दृष्टि एकतरफ़ा होती है' नियम से भी मेल खाता है</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr"/>
+      <c r="F6" s="17" t="inlineStr"/>
+    </row>
+    <row r="7" ht="62" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>उपाय-प्राथमिकता किस दशा से?</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>अभी विंशोत्तरी महादशा/अंतर्दशा से (+3/+2 — सबसे बड़े अंक)। आपने कहा था लाल किताब में विंशोत्तरी चलती ही नहीं।</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>35-साला लाल किताब दशा से; विंशोत्तरी हटा दूँ</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>⏱️ सबसे तेज़ रास्ता: तीनों पर 'सिफ़ारिश मान लो' लिख दें — मैं क्रम से ठीक करना शुरू कर दूँगा। हर 🟡 वाली चीज़ स्क्रीन पर 'अनुमानित' लिखकर दिखेगी।</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:E7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"सिफ़ारिश मान लो,बदलें,पता नहीं"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/LALKITAB_MASTER.xlsx
+++ b/docs/LALKITAB_MASTER.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>इंजन की जाँच — 18 खामियाँ, माप सहित</t>
+          <t>इंजन की जाँच — 22 खामियाँ, माप सहित</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -919,19 +919,19 @@
       <c r="A22" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>FAISLE</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>3 फ़ैसले जो बनाने से पहले चाहिए</t>
+          <t>3 फ़ैसले — तीनों तय हो गए ✅</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>🟡 जाँचें</t>
+          <t>🟢 पक्का</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1772,15 +1772,115 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="23" ht="62" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>गंभीर</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>स्वगृही भी असली राशि से जाँचा जा रहा है (F1 की तीसरी शाखा)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>उच्च/नीच के साथ-साथ 'स्वगृही' भी उसी गलत आधार पर है। टेवा से सही स्वगृही भाव: सूर्य 5 · चन्द्र 4 · मंगल 1, 8 · बुध 3, 6 · गुरु 9, 12 · शुक्र 2, 7 · शनि 10, 11। माप — तीनों दर्जे एक साथ: 46.0% ग्रह-पंक्तियाँ व 97.6% कुंडलियाँ बदलती हैं (केवल उच्च/नीच से 31.8% था)।</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>F1 के साथ ही ठीक होगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="62" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>गंभीर</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>उच्च-भंग के 9 नियम केवल दिखते हैं, लगते नहीं</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>uch_neech_niyam का bhang कॉलम स्क्रीन पर छपता है पर फलादेश में गिना नहीं जाता। नौ के नौ नियम गणना-योग्य हैं — सब 'अमुक ग्रह अमुक भाव में हो' के रूप में हैं (जैसे शनि: सूर्य या मंगल भाव 1 में हों तो शनि उच्च फल न देकर अत्यन्त कुप्रभाव देगा)। F1 तय होते ही ये सीधे लग सकते हैं।</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>'उच्च पर भंग' वाली अहम स्थिति पकड़ में आएगी</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="62" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>गंभीर</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>एक ही स्क्रीन पर एक ग्रह की दो अलग राशियाँ दिखती हैं</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>कुंडली-ग्रिड टेवा की स्थिर राशि दिखाता है (भाव 1 = मेष), पर ग्रह-कार्ड उसी ग्रह की असली गोचर राशि दिखाता है। आपने कहा 'लाल किताब में राशि always same रहती है' ⇒ कार्ड पर भी टेवा की राशि आनी चाहिए।</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>स्क्रीन का विरोधाभास हटेगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="62" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>अधूरा</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>ayuReadings में मंगल की राशि-आधारित जाँच की चौथी नकल</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>आयु-योग वाले हिस्से में मंगल का उच्च/स्वगृही अलग से, फिर उसी गलत राशि-आधार पर जाँचा जाता है।</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>F1 के साथ ही ठीक होगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>✅ अच्छी बात — ढाँचा मज़बूत है: डेटा अलग, गणना अलग, हर निष्कर्ष के साथ 'क्यों' दर्ज होता है, और उपाय का पूरा भंडार मौजूद है। 39 डेटा-खंडों में से ज़्यादातर सही हैं।</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>🎯 असली बात — गलतियाँ बिखरी नहीं, तीन जगह केंद्रित हैं: ① उच्च/नीच किस आधार पर ② दृष्टि व टक्कर की तालिका ③ उपाय-प्राथमिकता किस दशा से। ये तीन ठीक होते ही ऊपर की 18 में से 13 खामियाँ अपने-आप हल हो जाती हैं।</t>
         </is>
@@ -1790,8 +1890,8 @@
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1803,28 +1903,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🟡 3 फ़ैसले — इनके बिना मैं शुरू नहीं करूँगा</t>
+          <t>🟢 3 फ़ैसले — तीनों तय हो गए</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ये तीनों बड़े असर वाले हैं, इसलिए आपके शब्द के बिना कोड नहीं छूऊँगा।</t>
+          <t>आपके उत्तर नीचे दर्ज हैं। इन्हीं के अनुसार बनेगा — पर आपके कहे बिना शुरू नहीं करूँगा।</t>
         </is>
       </c>
     </row>
@@ -1841,26 +1940,21 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>बात क्या है</t>
+          <t>मेरी सिफ़ारिश थी</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>मेरी सिफ़ारिश</t>
+          <t>✅ आपका उत्तर (अंतिम)</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>आपका उत्तर</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>टिप्पणी</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="62" customHeight="1">
+          <t>इसका असर</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="76" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
           <t>F1</t>
@@ -1871,20 +1965,23 @@
           <t>उच्च/नीच किससे तय हो?</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>(क) टेवा के भाव से — भाव 1 = मेष, तो भाव 1 में बैठा सूर्य उच्च। (ख) ग्रह की असली गोचर राशि से — जैसा अभी कोड में है। असर: 32% ग्रह-पंक्तियाँ व 95% कुंडलियाँ बदलेंगी।</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>(क) भाव से — आपकी दी हुई सूची इसी रूप में थी</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr"/>
-      <c r="F5" s="17" t="inlineStr"/>
-    </row>
-    <row r="6" ht="62" customHeight="1">
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>(क) टेवा के भाव से</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>✅ टेवा के भाव से। लाल किताब में राशि हमेशा एक-सी रहती है — भाव 1 सदा मेष। (वैदिक में राशि व भाव दोनों से होता है, और वहाँ नीच-भंग जैसे और नियम भी लगते हैं — यदि एक में उच्च व दूसरे में नीच हो, ग्रह उसी स्थान में, तो नीच-भंग की स्थिति बनती है।)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>46.0% ग्रह-पंक्तियाँ · 97.6% कुंडलियाँ बदलेंगी (उच्च + नीच + स्वगृही तीनों)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
           <t>F2</t>
@@ -1895,20 +1992,23 @@
           <t>टक्कर किस दिशा में?</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>केवल 8वाँ (एकतरफ़ा, आपके कहे अनुसार), या 6ठा भी? अभी दोनों लगते हैं और आधे दंड बेवजह हैं।</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>केवल 8वाँ — यह आपके 'दृष्टि एकतरफ़ा होती है' नियम से भी मेल खाता है</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="62" customHeight="1">
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>केवल 8वाँ (एकतरफ़ा)</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>✅ केवल 8वाँ। हर ग्रह अपने से आठवें स्थान को टक्कर मारता है, छठे को नहीं। (दूसरी दृष्टि से देखें तो टक्कर मारने वाला ग्रह टक्कर खाने वाले से छठा बनेगा — पर खराब केवल आठवें वाला होता है, छठा नहीं।)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>आधे (50%) बेवजह के दंड हटेंगे; 99% कुंडलियाँ सुधरेंगी</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
           <t>F3</t>
@@ -1919,37 +2019,120 @@
           <t>उपाय-प्राथमिकता किस दशा से?</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>अभी विंशोत्तरी महादशा/अंतर्दशा से (+3/+2 — सबसे बड़े अंक)। आपने कहा था लाल किताब में विंशोत्तरी चलती ही नहीं।</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>35-साला लाल किताब दशा से; विंशोत्तरी हटा दूँ</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>⏱️ सबसे तेज़ रास्ता: तीनों पर 'सिफ़ारिश मान लो' लिख दें — मैं क्रम से ठीक करना शुरू कर दूँगा। हर 🟡 वाली चीज़ स्क्रीन पर 'अनुमानित' लिखकर दिखेगी।</t>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>35-साला दशा; विंशोत्तरी हटा दूँ ❌ (यह सिफ़ारिश गलत थी)</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>✅ दोनों प्रणालियाँ रहेंगी, अलग-अलग: लाल किताब के उपाय → 35-साला लाल किताब दशा से। वैदिक के उपाय → विंशोत्तरी से। यह सॉफ़्टवेयर दोनों तरह की कुंडली व दोनों तरह का फलादेश बनाता है — दोनों प्रणालियाँ अलग हैं।</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>विंशोत्तरी हटेगी नहीं — केवल लाल किताब वाले हिस्से से निकलेगी</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>🔎 F1 की स्वतंत्र पुष्टि — यह आपके शब्द के अलावा आपके अपने डेटा से भी सिद्ध होता है: uch_neech_niyam के भंग-नियम सब भावों में लिखे हैं, और सूर्य वाला नियम तो सीधे कहता है "सूर्य मेष में हो और सामने सातवें भाव (तुला) में…" — यानी मेष = वह स्थान, तुला = भाव 7। डेटा स्वयं राशि व भाव को एक ही मान रहा है। ✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>❓ एक छोटा सवाल जो F1 तय होने से निकला</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>विषय</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>डेटा क्या कहता है</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>आपकी सूची क्या कहती है</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>✏️ आपका उत्तर</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>राहु — भाव 6</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>भंग-नियम कहता है "कन्या राशि में होने पर भी शुभ फल नहीं" (कन्या = भाव 6)। साथ ही "राहु-बुध छठे हों तो शुभ फल"।</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>राहु उच्च = भाव 3 व 6 (दो भाव)</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr"/>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>केतु — भाव 12</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>भंग-नियम कहता है "मीन राशि में होने पर भी शुभ फल नहीं" (मीन = भाव 12)।</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>केतु उच्च = भाव 9 व 12 (दो भाव)</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr"/>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>मेरा पढ़ना: दोनों जगह ग्रह उच्च तो है, पर उच्च का फल नहीं मिलता — यानी यह अपने-आप में एक भंग है। दोनों नियम आपस में आईने जैसे हैं (राहु 6 ↔ केतु 12), इसलिए यह जानबूझकर लगता है। यदि यही सही है तो बस 'हाँ' लिख दें — मैं इन्हें 'उच्च पर भंग' के रूप में लगाऊँगा।</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:F9"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="E5:E7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"सिफ़ारिश मान लो,बदलें,पता नहीं"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
